--- a/stories/arbres/ATOM-SAN.MOV.001-04.xlsx
+++ b/stories/arbres/ATOM-SAN.MOV.001-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Malo a joué aux voitures dans le salon. Ses jambes bougent encore. Papa dit : on va dehors. Ils mettent les chaussures. Ils ouvrent la porte du jardin. L'herbe est fraîche. Un oiseau chante. Malo court jusqu'au cerisier. Papa reste près de lui. C'est un adulte. Malo lance un cerceau. Papa le renvoie. Malo dit : je joue dehors, avec un adulte. Parce qu'il a bougé, son corps est content. Ils boivent un peu d'eau. Plus tard, papa prend le sac. Ils vont au parc. Dehors, le vent est doux. Malo grimpe sur le petit pont en bois. Papa le voit. Malo court sur l'herbe du parc. Papa reste avec lui. Au jardin, puis au parc, c'est la même chose. On joue dehors un moment. On y va avec un adulte. Malo sent ses joues chaudes. Papa dit : encore un peu, puis on rentre. Malo donne le cerceau. Ils marchent ensemble.</t>
+          <t>Malo a joué aux voitures dans le salon. Ses jambes bougent encore. On va dehors. Ils mettent les chaussures. Ils ouvrent la porte du jardin. L'herbe est fraîche. Un oiseau chante. Malo court jusqu'au cerisier. Papa reste près de lui. C'est un adulte. Malo lance un cerceau. Papa le renvoie. Je joue dehors, avec un adulte. Parce qu'il a bougé, son corps est content. Ils boivent un peu d'eau. Plus tard, papa prend le sac. Ils vont au parc. Dehors, le vent est doux. Malo grimpe sur le petit pont en bois. Papa le voit. Malo court sur l'herbe du parc. Papa reste avec lui. Au jardin, puis au parc, c'est la même chose. On joue dehors un moment. On y va avec un adulte. Malo sent ses joues chaudes. Encore un peu, puis on rentre. Malo donne le cerceau. Ils marchent ensemble.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Malo a joué aux voitures dans le salon. Ses jambes bougent encore.
+papa|On va dehors.
+narrateur|Ils mettent les chaussures. Ils ouvrent la porte du jardin. L'herbe est fraîche. Un oiseau chante. Malo court jusqu'au cerisier. Papa reste près de lui. C'est un adulte. Malo lance un cerceau. Papa le renvoie.
+enfant-m|Je joue dehors, avec un adulte. Parce qu'il a bougé, son corps est content. Ils boivent un peu d'eau. Plus tard, papa prend le sac. Ils vont au parc. Dehors, le vent est doux.
+narrateur|Malo grimpe sur le petit pont en bois. Papa le voit. Malo court sur l'herbe du parc. Papa reste avec lui. Au jardin, puis au parc, c'est la même chose. On joue dehors un moment. On y va avec un adulte. Malo sent ses joues chaudes.
+papa|Encore un peu, puis on rentre.
+narrateur|Malo donne le cerceau. Ils marchent ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Malo veut bouger. Où joue-t-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1665,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Malo a joué dehors. D'abord au jardin. Puis au parc. Papa, un adulte, était avec lui.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1828,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Malo range ses chaussures. Il boit encore de l'eau. Merci, dit-il à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1995,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2035,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.MOV.001-04.xlsx
+++ b/stories/arbres/ATOM-SAN.MOV.001-04.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,11 @@
 narrateur|Malo donne le cerceau. Ils marchent ensemble.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1509,7 @@
           <t>narrateur|Malo veut bouger. Où joue-t-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1670,6 +1681,11 @@
           <t>narrateur|Malo a joué dehors. D'abord au jardin. Puis au parc. Papa, un adulte, était avec lui.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1849,7 @@
           <t>narrateur|Malo range ses chaussures. Il boit encore de l'eau. Merci, dit-il à papa.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2000,6 +2017,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2018,7 +2036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2042,6 +2060,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2243,6 +2275,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SAN.MOV.001-04.xlsx
+++ b/stories/arbres/ATOM-SAN.MOV.001-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Malo joue dehors deux fois</t>
+          <t>Les deux cerises</t>
         </is>
       </c>
     </row>
@@ -602,6 +602,11 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SAN.ALI.003</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -830,6 +835,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Deux cerises restent au cerisier. Raphaël joue d'abord au jardin, puis au parc. Papa est là. Deux dehors, la même chose : avec un adulte.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1189,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Malo a joué aux voitures dans le salon. Ses jambes bougent encore. On va dehors. Ils mettent les chaussures. Ils ouvrent la porte du jardin. L'herbe est fraîche. Un oiseau chante. Malo court jusqu'au cerisier. Papa reste près de lui. C'est un adulte. Malo lance un cerceau. Papa le renvoie. Je joue dehors, avec un adulte. Parce qu'il a bougé, son corps est content. Ils boivent un peu d'eau. Plus tard, papa prend le sac. Ils vont au parc. Dehors, le vent est doux. Malo grimpe sur le petit pont en bois. Papa le voit. Malo court sur l'herbe du parc. Papa reste avec lui. Au jardin, puis au parc, c'est la même chose. On joue dehors un moment. On y va avec un adulte. Malo sent ses joues chaudes. Encore un peu, puis on rentre. Malo donne le cerceau. Ils marchent ensemble.</t>
+          <t>Deux cerises rouges restent au cerisier. Elles brillent comme des perles. L'herbe du jardin est encore fraîche. Un oiseau picore plus bas. Les voitures de Raphaël dorment dans le salon. En ce moment, ses jambes bougent encore. Papa. On va dehors ? On va dehors. Ils mettent les chaussures. Ils ouvrent la porte du jardin. L'herbe chatouille les chevilles. Raphaël court jusqu'au cerisier. Papa reste près de lui. C'est un adulte. Raphaël lance un cerceau. Papa le renvoie. Le cerceau passe sous les deux cerises. Je joue dehors, avec un adulte. Bravo. Tu bouges, et je suis là. Parce qu'il a bougé, son corps est content. Ils boivent un peu d'eau. La gourde est fraîche. Plus tard, papa prend le sac. On va au parc, maintenant. Oui. Dehors, le vent est doux. Raphaël grimpe sur le petit pont en bois. Papa le voit. Le bois est lisse, un peu chaud. Raphaël court sur l'herbe du parc. Papa reste avec lui. Au jardin, puis au parc, c'est la même chose. On joue dehors un moment. On y va avec un adulte. Raphaël sent ses joues chaudes. Encore un peu, puis on rentre. Raphaël donne le cerceau. Ils marchent ensemble.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,18 +1329,51 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Malo a joué aux voitures dans le salon. Ses jambes bougent encore.
+          <t>narrateur|Deux cerises rouges restent au cerisier.
+narrateur|Elles brillent comme des perles.
+narrateur|L'herbe du jardin est encore fraîche.
+narrateur|Un oiseau picore plus bas.
+narrateur|Les voitures de Raphaël dorment dans le salon.
+narrateur|En ce moment, ses jambes bougent encore.
+enfant-m|Papa.
+enfant-m|On va dehors ?
 papa|On va dehors.
-narrateur|Ils mettent les chaussures. Ils ouvrent la porte du jardin. L'herbe est fraîche. Un oiseau chante. Malo court jusqu'au cerisier. Papa reste près de lui. C'est un adulte. Malo lance un cerceau. Papa le renvoie.
-enfant-m|Je joue dehors, avec un adulte. Parce qu'il a bougé, son corps est content. Ils boivent un peu d'eau. Plus tard, papa prend le sac. Ils vont au parc. Dehors, le vent est doux.
-narrateur|Malo grimpe sur le petit pont en bois. Papa le voit. Malo court sur l'herbe du parc. Papa reste avec lui. Au jardin, puis au parc, c'est la même chose. On joue dehors un moment. On y va avec un adulte. Malo sent ses joues chaudes.
+narrateur|Ils mettent les chaussures.
+narrateur|Ils ouvrent la porte du jardin.
+narrateur|L'herbe chatouille les chevilles.
+narrateur|Raphaël court jusqu'au cerisier.
+narrateur|Papa reste près de lui.
+narrateur|C'est un adulte.
+narrateur|Raphaël lance un cerceau.
+narrateur|Papa le renvoie.
+narrateur|Le cerceau passe sous les deux cerises.
+enfant-m|Je joue dehors, avec un adulte.
+papa|Bravo.
+papa|Tu bouges, et je suis là.
+narrateur|Parce qu'il a bougé, son corps est content.
+narrateur|Ils boivent un peu d'eau.
+narrateur|La gourde est fraîche.
+narrateur|Plus tard, papa prend le sac.
+papa|On va au parc, maintenant.
+enfant-m|Oui.
+narrateur|Dehors, le vent est doux.
+narrateur|Raphaël grimpe sur le petit pont en bois.
+narrateur|Papa le voit.
+narrateur|Le bois est lisse, un peu chaud.
+narrateur|Raphaël court sur l'herbe du parc.
+narrateur|Papa reste avec lui.
+narrateur|Au jardin, puis au parc, c'est la même chose.
+narrateur|On joue dehors un moment.
+narrateur|On y va avec un adulte.
+narrateur|Raphaël sent ses joues chaudes.
 papa|Encore un peu, puis on rentre.
-narrateur|Malo donne le cerceau. Ils marchent ensemble.</t>
+narrateur|Raphaël donne le cerceau.
+narrateur|Ils marchent ensemble.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>enfants_parc</t>
+          <t>enfants_parc,oiseau</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1400,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Malo veut bouger. Où joue-t-il ?</t>
+          <t>Raphaël veut bouger. Où joue-t-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1506,7 +1556,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Malo veut bouger. Où joue-t-il ?</t>
+          <t>narrateur|Raphaël veut bouger.
+narrateur|Où joue-t-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1534,7 +1585,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Malo a joué dehors. D'abord au jardin. Puis au parc. Papa, un adulte, était avec lui.</t>
+          <t>Raphaël a joué dehors. D'abord au jardin. Puis au parc. Papa, un adulte, était avec lui. Bravo. Tu as fait du bon travail. Deux fois dehors. Deux fois avec un adulte. Oui, papa. Le jardin, puis le parc. Le cerceau a un peu d'herbe des deux endroits. Raphaël le fait tourner. Il est le même. Tu as vu le petit pont ? Oui. Le bois était chaud. Papa pose une main sur l'épaule. Les joues de Raphaël sont encore chaudes.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1678,7 +1729,24 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Malo a joué dehors. D'abord au jardin. Puis au parc. Papa, un adulte, était avec lui.</t>
+          <t>narrateur|Raphaël a joué dehors.
+narrateur|D'abord au jardin.
+narrateur|Puis au parc.
+narrateur|Papa, un adulte, était avec lui.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+papa|Deux fois dehors.
+papa|Deux fois avec un adulte.
+enfant-m|Oui, papa.
+enfant-m|Le jardin, puis le parc.
+narrateur|Le cerceau a un peu d'herbe des deux endroits.
+narrateur|Raphaël le fait tourner.
+narrateur|Il est le même.
+papa|Tu as vu le petit pont ?
+enfant-m|Oui.
+enfant-m|Le bois était chaud.
+narrateur|Papa pose une main sur l'épaule.
+narrateur|Les joues de Raphaël sont encore chaudes.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1710,7 +1778,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Malo range ses chaussures. Il boit encore de l'eau. Merci, dit-il à papa.</t>
+          <t>Raphaël range ses chaussures. Un peu de terre du jardin. Un peu d'herbe du parc. Il boit encore de l'eau. La gourde fait un petit bruit. Merci, papa. Merci, Raphaël. Les deux cerises sont encore au cerisier. On les verra demain. D'accord. Papa pose le sac. Le cerceau retrouve le couloir. On reste un peu ensemble ? Oui, papa. La maison est calme. Les jambes de Raphaël sont contentes.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1846,7 +1914,22 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Malo range ses chaussures. Il boit encore de l'eau. Merci, dit-il à papa.</t>
+          <t>narrateur|Raphaël range ses chaussures.
+narrateur|Un peu de terre du jardin.
+narrateur|Un peu d'herbe du parc.
+narrateur|Il boit encore de l'eau.
+narrateur|La gourde fait un petit bruit.
+enfant-m|Merci, papa.
+papa|Merci, Raphaël.
+narrateur|Les deux cerises sont encore au cerisier.
+papa|On les verra demain.
+enfant-m|D'accord.
+narrateur|Papa pose le sac.
+narrateur|Le cerceau retrouve le couloir.
+papa|On reste un peu ensemble ?
+enfant-m|Oui, papa.
+narrateur|La maison est calme.
+narrateur|Les jambes de Raphaël sont contentes.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1874,7 +1957,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai joué dehors. Au jardin, puis au parc. Avec un adulte. Bravo. Tu as fait du bon travail. Les deux cerises ont regardé. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2014,7 +2097,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai joué dehors.
+enfant-m|Au jardin, puis au parc.
+enfant-m|Avec un adulte.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+papa|Les deux cerises ont regardé.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2036,7 +2125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2074,6 +2163,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.MOV.001-04.xlsx
+++ b/stories/arbres/ATOM-SAN.MOV.001-04.xlsx
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Malo a joué aux voitures dans le salon. Ses jambes bougent encore. Papa dit : on va &lt;emphasis level="moderate"&gt;dehors&lt;/emphasis&gt;. Ils mettent les chaussures. Ils ouvrent la porte du jardin. L'herbe est fraîche. Un oiseau chante. Malo court jusqu'au cerisier. Papa reste près de lui. C'est un adulte. Malo lance un cerceau. Papa le renvoie. Malo dit : je joue dehors, avec un adulte. Parce qu'il a bougé, son corps est content. Ils boivent un peu d'eau. Plus tard, papa prend le sac. Ils vont au parc. Dehors, le vent est doux. Malo grimpe sur le petit pont en bois. Papa le voit. Malo court sur l'herbe du parc. Papa reste avec lui. Au jardin, puis au parc, c'est la même chose. On joue dehors un moment. On y va avec un adulte. Malo sent ses joues chaudes. Papa dit : encore un peu, puis on rentre. Malo donne le cerceau. Ils marchent ensemble.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Deux cerises rouges restent au cerisier. Elles brillent comme des perles. L'herbe du jardin est encore fraîche. Un oiseau picore plus bas. Les voitures de Raphaël dorment dans le salon. En ce moment, ses jambes bougent encore. Papa. On va dehors ? On va dehors. Ils mettent les chaussures. Ils ouvrent la porte du jardin. L'herbe chatouille les chevilles. Raphaël court jusqu'au cerisier. Papa reste près de lui. C'est un adulte. Raphaël lance un cerceau. Papa le renvoie. Le cerceau passe sous les deux cerises. Je joue dehors, avec un adulte. Bravo. Tu bouges, et je suis là. Parce qu'il a bougé, son corps est content. Ils boivent un peu d'eau. La gourde est fraîche. Plus tard, papa prend le sac. On va au parc, maintenant. Oui. Dehors, le vent est doux. Raphaël grimpe sur le petit pont en bois. Papa le voit. Le bois est lisse, un peu chaud. Raphaël court sur l'herbe du parc. Papa reste avec lui. Au jardin, puis au parc, c'est la même chose. On joue dehors un moment. On y va avec un adulte. Raphaël sent ses joues chaudes. Encore un peu, puis on rentre. Raphaël donne le cerceau. Ils marchent ensemble.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Malo veut bouger. Où joue-t-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël veut bouger. Où joue-t-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1560,7 +1560,6 @@
 narrateur|Où joue-t-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1585,12 +1584,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a joué dehors. D'abord au jardin. Puis au parc. Papa, un adulte, était avec lui. Bravo. Tu as fait du bon travail. Deux fois dehors. Deux fois avec un adulte. Oui, papa. Le jardin, puis le parc. Le cerceau a un peu d'herbe des deux endroits. Raphaël le fait tourner. Il est le même. Tu as vu le petit pont ? Oui. Le bois était chaud. Papa pose une main sur l'épaule. Les joues de Raphaël sont encore chaudes.</t>
+          <t>Raphaël a joué dehors. D'abord au jardin. Puis au parc. Papa, un adulte, était avec lui. Bravo. Deux fois dehors. Deux fois avec un adulte. Oui, papa. Le jardin, puis le parc. Le cerceau a un peu d'herbe des deux endroits. Raphaël le fait tourner. Il est le même. Tu as vu le petit pont ? Oui. Le bois était chaud. Papa pose une main sur l'épaule. Les joues de Raphaël sont encore chaudes.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Malo a joué &lt;emphasis level="moderate"&gt;dehors&lt;/emphasis&gt;. D'abord au jardin. Puis au parc. Papa, un adulte, était avec lui.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël a joué dehors. D'abord au jardin. Puis au parc. Papa, un adulte, était avec lui. Bravo. Deux fois dehors. Deux fois avec un adulte. Oui, papa. Le jardin, puis le parc. Le cerceau a un peu d'herbe des deux endroits. Raphaël le fait tourner. Il est le même. Tu as vu le petit pont ? Oui. Le bois était chaud. Papa pose une main sur l'épaule. Les joues de Raphaël sont encore chaudes.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1734,7 +1733,6 @@
 narrateur|Puis au parc.
 narrateur|Papa, un adulte, était avec lui.
 papa|Bravo.
-papa|Tu as fait du bon travail.
 papa|Deux fois dehors.
 papa|Deux fois avec un adulte.
 enfant-m|Oui, papa.
@@ -1783,7 +1781,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Malo range ses chaussures. Il boit encore de l'eau. Merci, dit-il à papa.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël range ses chaussures. Un peu de terre du jardin. Un peu d'herbe du parc. Il boit encore de l'eau. La gourde fait un petit bruit. Merci, papa. Merci, Raphaël. Les deux cerises sont encore au cerisier. On les verra demain. D'accord. Papa pose le sac. Le cerceau retrouve le couloir. On reste un peu ensemble ? Oui, papa. La maison est calme. Les jambes de Raphaël sont contentes.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1932,7 +1930,6 @@
 narrateur|Les jambes de Raphaël sont contentes.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,12 +1954,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai joué dehors. Au jardin, puis au parc. Avec un adulte. Bravo. Tu as fait du bon travail. Les deux cerises ont regardé. L'histoire est finie.</t>
+          <t>J'ai joué dehors. Au jardin, puis au parc. Avec un adulte. Bravo. Les deux cerises ont regardé.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai joué dehors. Au jardin, puis au parc. Avec un adulte. Bravo. Les deux cerises ont regardé.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2101,12 +2098,9 @@
 enfant-m|Au jardin, puis au parc.
 enfant-m|Avec un adulte.
 papa|Bravo.
-papa|Tu as fait du bon travail.
-papa|Les deux cerises ont regardé.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+papa|Les deux cerises ont regardé.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2125,7 +2119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2170,6 +2164,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.MOV.001-04.xlsx
+++ b/stories/arbres/ATOM-SAN.MOV.001-04.xlsx
@@ -688,7 +688,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Malo, papa</t>
+          <t>Raphaël, papa</t>
         </is>
       </c>
     </row>
